--- a/artfynd/A 20313-2026 artfynd.xlsx
+++ b/artfynd/A 20313-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133042754</v>
       </c>
       <c r="B3" t="n">
-        <v>103417</v>
+        <v>103419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20313-2026 artfynd.xlsx
+++ b/artfynd/A 20313-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133042754</v>
       </c>
       <c r="B3" t="n">
-        <v>103419</v>
+        <v>103427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20313-2026 artfynd.xlsx
+++ b/artfynd/A 20313-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,6 +881,115 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134088281</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Satserup A 21313-2026, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>423256</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6192667</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hörby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Äspinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20313-2026 artfynd.xlsx
+++ b/artfynd/A 20313-2026 artfynd.xlsx
@@ -886,7 +886,7 @@
         <v>134088281</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,14 +926,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Satserup A 21313-2026, Sk</t>
+          <t>Satserup A 20313-2026, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>423256</v>
       </c>
       <c r="R4" t="n">
-        <v>6192667</v>
+        <v>6192668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 20313-2026 artfynd.xlsx
+++ b/artfynd/A 20313-2026 artfynd.xlsx
@@ -886,7 +886,7 @@
         <v>134088281</v>
       </c>
       <c r="B4" t="n">
-        <v>57978</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
